--- a/docs/tables/m3c2_final_six.xlsx
+++ b/docs/tables/m3c2_final_six.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>registration error (mm)</t>
+          <t>registration error (cm)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>19.28</v>
+        <v>1.93</v>
       </c>
       <c r="F2" t="n">
         <v>23768</v>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>19.75</v>
+        <v>1.98</v>
       </c>
       <c r="F3" t="n">
         <v>26890</v>
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>19.08</v>
+        <v>1.91</v>
       </c>
       <c r="F4" t="n">
         <v>62241</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>20.04</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>224339</v>
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>14.82</v>
+        <v>1.48</v>
       </c>
       <c r="F6" t="n">
         <v>4522</v>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15.7</v>
+        <v>1.57</v>
       </c>
       <c r="F7" t="n">
         <v>4545</v>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>16.09</v>
+        <v>1.61</v>
       </c>
       <c r="F8" t="n">
         <v>6208</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>19.77</v>
+        <v>1.98</v>
       </c>
       <c r="F9" t="n">
         <v>10527</v>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>19.87</v>
+        <v>1.99</v>
       </c>
       <c r="F10" t="n">
         <v>12287</v>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>21.7</v>
+        <v>2.17</v>
       </c>
       <c r="F11" t="n">
         <v>11498</v>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>19.55</v>
+        <v>1.96</v>
       </c>
       <c r="F12" t="n">
         <v>14753</v>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>20.86</v>
+        <v>2.09</v>
       </c>
       <c r="F13" t="n">
         <v>28144</v>
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>12.68</v>
+        <v>1.27</v>
       </c>
       <c r="F14" t="n">
         <v>975</v>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>12.19</v>
+        <v>1.22</v>
       </c>
       <c r="F15" t="n">
         <v>1093</v>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12.82</v>
+        <v>1.28</v>
       </c>
       <c r="F16" t="n">
         <v>1313</v>
@@ -1440,7 +1440,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>14.65</v>
+        <v>1.47</v>
       </c>
       <c r="F17" t="n">
         <v>2062</v>
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.59</v>
+        <v>1.16</v>
       </c>
       <c r="F18" t="n">
         <v>2423</v>
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>13</v>
+        <v>1.3</v>
       </c>
       <c r="F19" t="n">
         <v>2113</v>
@@ -1623,7 +1623,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>16.84</v>
+        <v>1.68</v>
       </c>
       <c r="F20" t="n">
         <v>7804</v>
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>17.59</v>
+        <v>1.76</v>
       </c>
       <c r="F21" t="n">
         <v>30648</v>
@@ -1745,7 +1745,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>17.77</v>
+        <v>1.78</v>
       </c>
       <c r="F22" t="n">
         <v>4356</v>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>16.59</v>
+        <v>1.66</v>
       </c>
       <c r="F23" t="n">
         <v>4115</v>
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>17.87</v>
+        <v>1.79</v>
       </c>
       <c r="F24" t="n">
         <v>16734</v>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>18.17</v>
+        <v>1.82</v>
       </c>
       <c r="F25" t="n">
         <v>24244</v>
